--- a/data/CRPL_All_Data_Exactly_20.xlsx
+++ b/data/CRPL_All_Data_Exactly_20.xlsx
@@ -332,6 +332,20 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:E23" totalsRowShown="0">
+  <autoFilter ref="A1:E23"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="CRF No"/>
+    <tableColumn id="2" name="CRF Name"/>
+    <tableColumn id="3" name="Stage"/>
+    <tableColumn id="4" name="CRPL Remarks"/>
+    <tableColumn id="5" name="NBP Remarks"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -622,8 +636,9 @@
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="9.42578125" customWidth="1"/>
     <col min="2" max="2" width="80.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="97.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="172.5703125" bestFit="1" customWidth="1"/>
   </cols>
@@ -1018,5 +1033,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/data/CRPL_All_Data_Exactly_20.xlsx
+++ b/data/CRPL_All_Data_Exactly_20.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="91">
   <si>
     <t>CRF No</t>
   </si>
@@ -234,9 +234,6 @@
     <t xml:space="preserve">We cant confirm about R-22 Logs now </t>
   </si>
   <si>
-    <t>ISD issue is still OPEN on SIEM</t>
-  </si>
-  <si>
     <t>704-26</t>
   </si>
   <si>
@@ -280,6 +277,21 @@
   </si>
   <si>
     <t>No CRF</t>
+  </si>
+  <si>
+    <t>UAT patch is awaited from CRPL.</t>
+  </si>
+  <si>
+    <t>Will Deliver this CRF at max by 18-Sep ,UAT patch is awaited from CRPL.</t>
+  </si>
+  <si>
+    <t>Will Deliver this CRF at max by 18-Sep, UAT patch is awaited from CRPL.</t>
+  </si>
+  <si>
+    <t>No Update.</t>
+  </si>
+  <si>
+    <t>ISD issue is still OPEN on SIEM, Response still awaited from CRPL.</t>
   </si>
 </sst>
 </file>
@@ -335,8 +347,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:E23" totalsRowShown="0">
-  <autoFilter ref="A1:E23"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:E22" totalsRowShown="0">
+  <autoFilter ref="A1:E22"/>
   <tableColumns count="5">
     <tableColumn id="1" name="CRF No"/>
     <tableColumn id="2" name="CRF Name"/>
@@ -633,13 +645,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
     <col min="2" max="2" width="80.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="97.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="97.5703125" customWidth="1"/>
     <col min="5" max="5" width="172.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -725,7 +737,7 @@
         <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -742,7 +754,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -815,10 +827,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
         <v>38</v>
@@ -827,15 +839,15 @@
         <v>25</v>
       </c>
       <c r="E11" t="s">
-        <v>25</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
         <v>38</v>
@@ -844,191 +856,177 @@
         <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="E13" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E14" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B15" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D15" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E15" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D16" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="E16" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B17" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="D17" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E17" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C18" t="s">
         <v>52</v>
       </c>
       <c r="D18" t="s">
-        <v>67</v>
+        <v>70</v>
+      </c>
+      <c r="E18" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B19" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="D19" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E19" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="D20" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E20" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C21" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="D21" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E21" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="D22" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E22" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>86</v>
-      </c>
-      <c r="B23" t="s">
-        <v>83</v>
-      </c>
-      <c r="C23" t="s">
-        <v>52</v>
-      </c>
-      <c r="D23" t="s">
         <v>84</v>
-      </c>
-      <c r="E23" t="s">
-        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/data/CRPL_All_Data_Exactly_20.xlsx
+++ b/data/CRPL_All_Data_Exactly_20.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="102">
   <si>
     <t>CRF No</t>
   </si>
@@ -84,9 +84,6 @@
     <t>TBD</t>
   </si>
   <si>
-    <t>Approval Received on 7-Sep</t>
-  </si>
-  <si>
     <t>Response Awaited from CRPL</t>
   </si>
   <si>
@@ -96,9 +93,6 @@
     <t>Automation of Encrypted Payment File Upload via Email in SMARTPAY Back Office Portal</t>
   </si>
   <si>
-    <t xml:space="preserve">Will Deliver this CRF at max by 18-Sep </t>
-  </si>
-  <si>
     <t>727-26</t>
   </si>
   <si>
@@ -213,9 +207,6 @@
     <t xml:space="preserve">Please confirm UAT Completion </t>
   </si>
   <si>
-    <t>UNDER UAT</t>
-  </si>
-  <si>
     <t>749-25</t>
   </si>
   <si>
@@ -282,16 +273,58 @@
     <t>UAT patch is awaited from CRPL.</t>
   </si>
   <si>
-    <t>Will Deliver this CRF at max by 18-Sep ,UAT patch is awaited from CRPL.</t>
-  </si>
-  <si>
     <t>Will Deliver this CRF at max by 18-Sep, UAT patch is awaited from CRPL.</t>
   </si>
   <si>
     <t>No Update.</t>
   </si>
   <si>
-    <t>ISD issue is still OPEN on SIEM, Response still awaited from CRPL.</t>
+    <t>Mobile App X SMARTPAY for Dealer Collection</t>
+  </si>
+  <si>
+    <t>Reuested objects provided by NBP team on 4th September</t>
+  </si>
+  <si>
+    <t>735-26</t>
+  </si>
+  <si>
+    <t>722-26</t>
+  </si>
+  <si>
+    <t>OUTWARD Remittance Dated 4th May-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Waiting for detail BRD from OPG </t>
+  </si>
+  <si>
+    <t>Internal approval received but NBP approval is still pendin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will Revert </t>
+  </si>
+  <si>
+    <t>QA in process and will try to send UAT patch at max by 22-Sep CO</t>
+  </si>
+  <si>
+    <t>UAT Patch Shared</t>
+  </si>
+  <si>
+    <t>Recived.</t>
+  </si>
+  <si>
+    <t>Will share delivery time line as  above three CRF's moved on UAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIT completed will share delivery time line this week </t>
+  </si>
+  <si>
+    <t>UNDER UAT, discussion required with qasim</t>
+  </si>
+  <si>
+    <t>ISD issue is still OPEN on SIEM, meeting will be held between is and crpl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ad changes </t>
   </si>
 </sst>
 </file>
@@ -347,8 +380,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:E22" totalsRowShown="0">
-  <autoFilter ref="A1:E22"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:E26" totalsRowShown="0">
+  <autoFilter ref="A1:E26"/>
   <tableColumns count="5">
     <tableColumn id="1" name="CRF No"/>
     <tableColumn id="2" name="CRF Name"/>
@@ -645,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -734,299 +767,355 @@
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
         <v>23</v>
       </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
       </c>
       <c r="D7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E7" t="s">
         <v>21</v>
-      </c>
-      <c r="E7" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
         <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
         <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
         <v>36</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10" t="s">
         <v>37</v>
       </c>
-      <c r="C10" t="s">
+      <c r="E10" t="s">
         <v>38</v>
-      </c>
-      <c r="D10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="E11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="E12" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" t="s">
         <v>45</v>
       </c>
-      <c r="B13" t="s">
+      <c r="D13" t="s">
         <v>46</v>
       </c>
-      <c r="C13" t="s">
+      <c r="E13" t="s">
         <v>47</v>
-      </c>
-      <c r="D13" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" t="s">
         <v>50</v>
       </c>
-      <c r="B14" t="s">
+      <c r="D14" t="s">
         <v>51</v>
       </c>
-      <c r="C14" t="s">
+      <c r="E14" t="s">
         <v>52</v>
-      </c>
-      <c r="D14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" t="s">
         <v>55</v>
       </c>
-      <c r="B15" t="s">
+      <c r="D15" t="s">
         <v>56</v>
       </c>
-      <c r="C15" t="s">
+      <c r="E15" t="s">
         <v>57</v>
-      </c>
-      <c r="D15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E15" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" t="s">
         <v>60</v>
       </c>
-      <c r="B16" t="s">
+      <c r="D16" t="s">
         <v>61</v>
       </c>
-      <c r="C16" t="s">
-        <v>62</v>
-      </c>
-      <c r="D16" t="s">
-        <v>63</v>
-      </c>
       <c r="E16" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E17" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E18" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="D19" t="s">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="E19" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>76</v>
+        <v>7</v>
       </c>
       <c r="D20" t="s">
-        <v>77</v>
+        <v>7</v>
       </c>
       <c r="E20" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D21" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="E21" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="B22" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" t="s">
+        <v>70</v>
+      </c>
+      <c r="E22" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>71</v>
+      </c>
+      <c r="B23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" t="s">
+        <v>74</v>
+      </c>
+      <c r="E23" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" t="s">
+        <v>60</v>
+      </c>
+      <c r="D24" t="s">
+        <v>77</v>
+      </c>
+      <c r="E24" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>82</v>
       </c>
-      <c r="C22" t="s">
-        <v>52</v>
-      </c>
-      <c r="D22" t="s">
-        <v>83</v>
-      </c>
-      <c r="E22" t="s">
-        <v>84</v>
+      <c r="B25" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/data/CRPL_All_Data_Exactly_20.xlsx
+++ b/data/CRPL_All_Data_Exactly_20.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="115">
   <si>
     <t>CRF No</t>
   </si>
@@ -267,9 +267,6 @@
     <t>Waiting to hear from CRPL</t>
   </si>
   <si>
-    <t>No CRF</t>
-  </si>
-  <si>
     <t>UAT patch is awaited from CRPL.</t>
   </si>
   <si>
@@ -324,7 +321,49 @@
     <t>ISD issue is still OPEN on SIEM, meeting will be held between is and crpl</t>
   </si>
   <si>
-    <t xml:space="preserve">Ad changes </t>
+    <t>Prefix issue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resend Interface </t>
+  </si>
+  <si>
+    <t>Observation shared with CRPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBCS late Response Update </t>
+  </si>
+  <si>
+    <t>UBCS CBA Posting Error</t>
+  </si>
+  <si>
+    <t>99 Timeout in IBFT title fetch NRSP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raast Batch Status Update </t>
+  </si>
+  <si>
+    <t>RAAST OTC Reversal</t>
+  </si>
+  <si>
+    <t>RE attempt title fetch</t>
+  </si>
+  <si>
+    <t>Muneeb</t>
+  </si>
+  <si>
+    <t>Mubashir</t>
+  </si>
+  <si>
+    <t>Jawwad sb</t>
+  </si>
+  <si>
+    <t>Saad/Ubaid</t>
+  </si>
+  <si>
+    <t>Saad/Muneeb</t>
+  </si>
+  <si>
+    <t>Saad/1 Link</t>
   </si>
 </sst>
 </file>
@@ -380,8 +419,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:E26" totalsRowShown="0">
-  <autoFilter ref="A1:E26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:E34" totalsRowShown="0">
+  <autoFilter ref="A1:E34"/>
   <tableColumns count="5">
     <tableColumn id="1" name="CRF No"/>
     <tableColumn id="2" name="CRF Name"/>
@@ -678,10 +717,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="80.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
     <col min="4" max="4" width="97.5703125" customWidth="1"/>
@@ -767,10 +806,10 @@
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -784,10 +823,10 @@
         <v>50</v>
       </c>
       <c r="D6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" t="s">
         <v>95</v>
-      </c>
-      <c r="E6" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -801,7 +840,7 @@
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E7" t="s">
         <v>21</v>
@@ -869,10 +908,10 @@
         <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -886,10 +925,10 @@
         <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -957,7 +996,7 @@
         <v>61</v>
       </c>
       <c r="E16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -974,7 +1013,7 @@
         <v>64</v>
       </c>
       <c r="E17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -991,15 +1030,15 @@
         <v>67</v>
       </c>
       <c r="E18" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
         <v>7</v>
@@ -1008,15 +1047,15 @@
         <v>7</v>
       </c>
       <c r="E19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" t="s">
         <v>89</v>
-      </c>
-      <c r="B20" t="s">
-        <v>90</v>
       </c>
       <c r="C20" t="s">
         <v>7</v>
@@ -1025,7 +1064,7 @@
         <v>7</v>
       </c>
       <c r="E20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1039,10 +1078,10 @@
         <v>50</v>
       </c>
       <c r="D21" t="s">
+        <v>91</v>
+      </c>
+      <c r="E21" t="s">
         <v>92</v>
-      </c>
-      <c r="E21" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -1098,7 +1137,7 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="B25" t="s">
         <v>79</v>
@@ -1114,8 +1153,108 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>112</v>
+      </c>
       <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>113</v>
+      </c>
+      <c r="B27" t="s">
         <v>101</v>
+      </c>
+      <c r="C27" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>113</v>
+      </c>
+      <c r="B28" t="s">
+        <v>103</v>
+      </c>
+      <c r="C28" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" t="s">
+        <v>104</v>
+      </c>
+      <c r="C29" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>114</v>
+      </c>
+      <c r="B30" t="s">
+        <v>105</v>
+      </c>
+      <c r="C30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>113</v>
+      </c>
+      <c r="B31" t="s">
+        <v>106</v>
+      </c>
+      <c r="C31" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>109</v>
+      </c>
+      <c r="B32" t="s">
+        <v>106</v>
+      </c>
+      <c r="C32" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>110</v>
+      </c>
+      <c r="B33" t="s">
+        <v>107</v>
+      </c>
+      <c r="C33" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>110</v>
+      </c>
+      <c r="B34" t="s">
+        <v>108</v>
+      </c>
+      <c r="C34" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/data/CRPL_All_Data_Exactly_20.xlsx
+++ b/data/CRPL_All_Data_Exactly_20.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="105">
   <si>
     <t>CRF No</t>
   </si>
@@ -333,37 +333,7 @@
     <t xml:space="preserve">UBCS late Response Update </t>
   </si>
   <si>
-    <t>UBCS CBA Posting Error</t>
-  </si>
-  <si>
     <t>99 Timeout in IBFT title fetch NRSP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raast Batch Status Update </t>
-  </si>
-  <si>
-    <t>RAAST OTC Reversal</t>
-  </si>
-  <si>
-    <t>RE attempt title fetch</t>
-  </si>
-  <si>
-    <t>Muneeb</t>
-  </si>
-  <si>
-    <t>Mubashir</t>
-  </si>
-  <si>
-    <t>Jawwad sb</t>
-  </si>
-  <si>
-    <t>Saad/Ubaid</t>
-  </si>
-  <si>
-    <t>Saad/Muneeb</t>
-  </si>
-  <si>
-    <t>Saad/1 Link</t>
   </si>
 </sst>
 </file>
@@ -717,7 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -1136,9 +1106,6 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>111</v>
-      </c>
       <c r="B25" t="s">
         <v>79</v>
       </c>
@@ -1153,11 +1120,8 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>112</v>
-      </c>
       <c r="B26" t="s">
-        <v>42</v>
+        <v>104</v>
       </c>
       <c r="C26" t="s">
         <v>45</v>
@@ -1167,9 +1131,6 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>113</v>
-      </c>
       <c r="B27" t="s">
         <v>101</v>
       </c>
@@ -1181,79 +1142,10 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>113</v>
-      </c>
       <c r="B28" t="s">
         <v>103</v>
       </c>
       <c r="C28" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>113</v>
-      </c>
-      <c r="B29" t="s">
-        <v>104</v>
-      </c>
-      <c r="C29" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>114</v>
-      </c>
-      <c r="B30" t="s">
-        <v>105</v>
-      </c>
-      <c r="C30" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>113</v>
-      </c>
-      <c r="B31" t="s">
-        <v>106</v>
-      </c>
-      <c r="C31" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>109</v>
-      </c>
-      <c r="B32" t="s">
-        <v>106</v>
-      </c>
-      <c r="C32" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>110</v>
-      </c>
-      <c r="B33" t="s">
-        <v>107</v>
-      </c>
-      <c r="C33" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>110</v>
-      </c>
-      <c r="B34" t="s">
-        <v>108</v>
-      </c>
-      <c r="C34" t="s">
         <v>57</v>
       </c>
     </row>
